--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -603,6 +603,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -612,7 +615,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -773,6 +776,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -816,7 +822,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -978,6 +984,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -987,7 +996,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1149,6 +1158,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>15523855.279351614</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15858152.82628401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1191,7 +1203,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1353,6 +1365,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1362,7 +1377,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1524,6 +1539,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5085531.097460622</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5419828.6443930175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1545,11 +1563,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443522048"/>
-        <c:axId val="466713216"/>
+        <c:axId val="78679424"/>
+        <c:axId val="92018176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443522048"/>
+        <c:axId val="78679424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1592,14 +1610,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="466713216"/>
+        <c:crossAx val="92018176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="466713216"/>
+        <c:axId val="92018176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1650,7 +1668,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443522048"/>
+        <c:crossAx val="78679424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1811,7 +1829,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1973,6 +1991,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-127166.75771952557</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-218860.88907832516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1987,8 +2008,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="474833664"/>
-        <c:axId val="474495232"/>
+        <c:axId val="522732288"/>
+        <c:axId val="521972736"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2013,7 +2034,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2175,6 +2196,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2184,7 +2208,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2346,6 +2370,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2362,11 +2389,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469383808"/>
-        <c:axId val="474493312"/>
+        <c:axId val="447632896"/>
+        <c:axId val="521971200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469383808"/>
+        <c:axId val="447632896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2409,14 +2436,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474493312"/>
+        <c:crossAx val="521971200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="474493312"/>
+        <c:axId val="521971200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2467,12 +2494,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469383808"/>
+        <c:crossAx val="447632896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="474495232"/>
+        <c:axId val="521972736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2509,12 +2536,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474833664"/>
+        <c:crossAx val="522732288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="474833664"/>
+        <c:axId val="522732288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2523,7 +2550,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="474495232"/>
+        <c:crossAx val="521972736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2932,7 +2959,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5490,6 +5517,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:13" ht="12.75">
+      <c r="A57" s="11">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="12">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="12">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="13">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="13">
+        <v>-218860.88907832516</v>
+      </c>
+      <c r="F57" s="14">
+        <v>-205696.32229368878</v>
+      </c>
+      <c r="G57" s="14">
+        <v>13723339.905224066</v>
+      </c>
+      <c r="H57" s="14">
+        <v>14601633.803121971</v>
+      </c>
+      <c r="I57" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J57" s="14">
+        <v>15858152.82628401</v>
+      </c>
+      <c r="K57" s="14">
+        <v>5419828.6443930175</v>
+      </c>
+      <c r="L57" s="13">
+        <v>1256519.0231620383</v>
+      </c>
+      <c r="M57" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -606,6 +606,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -615,7 +618,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -779,6 +782,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -822,7 +828,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -987,6 +993,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -996,7 +1005,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1161,6 +1170,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15858152.82628401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15967939.768014949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1203,7 +1215,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1368,6 +1380,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,7 +1392,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1542,6 +1557,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5419828.6443930175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5529615.5861239564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1563,11 +1581,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78679424"/>
-        <c:axId val="92018176"/>
+        <c:axId val="104017280"/>
+        <c:axId val="397240960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78679424"/>
+        <c:axId val="104017280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1610,14 +1628,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92018176"/>
+        <c:crossAx val="397240960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92018176"/>
+        <c:axId val="397240960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1668,7 +1686,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78679424"/>
+        <c:crossAx val="104017280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1829,7 +1847,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1994,6 +2012,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-218860.88907832516</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-259981.61012664012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2008,8 +2029,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522732288"/>
-        <c:axId val="521972736"/>
+        <c:axId val="543792128"/>
+        <c:axId val="543790208"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2034,7 +2055,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2199,6 +2220,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2208,7 +2232,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2373,6 +2397,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2389,11 +2416,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="447632896"/>
-        <c:axId val="521971200"/>
+        <c:axId val="530589184"/>
+        <c:axId val="530590720"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="447632896"/>
+        <c:axId val="530589184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2436,14 +2463,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521971200"/>
+        <c:crossAx val="530590720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521971200"/>
+        <c:axId val="530590720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2494,12 +2521,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447632896"/>
+        <c:crossAx val="530589184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="521972736"/>
+        <c:axId val="543790208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2536,12 +2563,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522732288"/>
+        <c:crossAx val="543792128"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522732288"/>
+        <c:axId val="543792128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2550,7 +2577,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="521972736"/>
+        <c:crossAx val="543790208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2959,7 +2986,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5558,6 +5585,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:13" ht="12.75">
+      <c r="A58" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="12">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="12">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="13">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="13">
+        <v>-259981.61012664012</v>
+      </c>
+      <c r="F58" s="14">
+        <v>-242520.15265919158</v>
+      </c>
+      <c r="G58" s="14">
+        <v>13480819.752564875</v>
+      </c>
+      <c r="H58" s="14">
+        <v>14451439.134726271</v>
+      </c>
+      <c r="I58" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J58" s="14">
+        <v>15967939.768014949</v>
+      </c>
+      <c r="K58" s="14">
+        <v>5529615.5861239564</v>
+      </c>
+      <c r="L58" s="13">
+        <v>1516500.6332886785</v>
+      </c>
+      <c r="M58" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -609,6 +609,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -618,7 +621,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -785,6 +788,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -828,7 +834,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -996,6 +1002,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1005,7 +1014,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1173,6 +1182,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15967939.768014949</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16008382.510111498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1215,7 +1227,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1383,6 +1395,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1392,7 +1407,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1560,6 +1575,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5529615.5861239564</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5570058.3282205053</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1581,11 +1599,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="104017280"/>
-        <c:axId val="397240960"/>
+        <c:axId val="81973632"/>
+        <c:axId val="81975552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="104017280"/>
+        <c:axId val="81973632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1628,14 +1646,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397240960"/>
+        <c:crossAx val="81975552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="397240960"/>
+        <c:axId val="81975552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1686,7 +1704,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="104017280"/>
+        <c:crossAx val="81973632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1847,7 +1865,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2015,6 +2033,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-259981.61012664012</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-239860.56658340184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2029,8 +2050,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="543792128"/>
-        <c:axId val="543790208"/>
+        <c:axId val="438347264"/>
+        <c:axId val="436426624"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2055,7 +2076,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2223,6 +2244,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2232,7 +2256,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2400,6 +2424,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2416,11 +2443,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530589184"/>
-        <c:axId val="530590720"/>
+        <c:axId val="423729024"/>
+        <c:axId val="436425088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530589184"/>
+        <c:axId val="423729024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2463,14 +2490,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530590720"/>
+        <c:crossAx val="436425088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530590720"/>
+        <c:axId val="436425088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2521,12 +2548,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530589184"/>
+        <c:crossAx val="423729024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="543790208"/>
+        <c:axId val="436426624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2563,12 +2590,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543792128"/>
+        <c:crossAx val="438347264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="543792128"/>
+        <c:axId val="438347264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2577,7 +2604,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="543790208"/>
+        <c:crossAx val="436426624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2986,7 +3013,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5626,6 +5653,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:13" ht="12.75">
+      <c r="A59" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="12">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="12">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="13">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="13">
+        <v>-239860.56658340184</v>
+      </c>
+      <c r="F59" s="14">
+        <v>-223126.09855248407</v>
+      </c>
+      <c r="G59" s="14">
+        <v>13257693.654012391</v>
+      </c>
+      <c r="H59" s="14">
+        <v>14252021.310239417</v>
+      </c>
+      <c r="I59" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J59" s="14">
+        <v>16008382.510111498</v>
+      </c>
+      <c r="K59" s="14">
+        <v>5570058.3282205053</v>
+      </c>
+      <c r="L59" s="13">
+        <v>1756361.1998720802</v>
+      </c>
+      <c r="M59" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -612,6 +612,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -621,7 +624,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -791,6 +794,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -834,7 +840,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1005,6 +1011,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1014,7 +1023,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1185,6 +1194,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>16008382.510111498</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>15650423.858476061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,7 +1239,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1398,6 +1410,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1407,7 +1422,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1578,6 +1593,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5570058.3282205053</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5212099.6765850689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1599,11 +1617,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="81973632"/>
-        <c:axId val="81975552"/>
+        <c:axId val="367295872"/>
+        <c:axId val="385508864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="81973632"/>
+        <c:axId val="367295872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1646,14 +1664,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81975552"/>
+        <c:crossAx val="385508864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81975552"/>
+        <c:axId val="385508864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1704,7 +1722,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81973632"/>
+        <c:crossAx val="367295872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1865,7 +1883,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2036,6 +2054,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-239860.56658340184</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-153850.30177591741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2050,8 +2071,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="438347264"/>
-        <c:axId val="436426624"/>
+        <c:axId val="417356800"/>
+        <c:axId val="417354496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2076,7 +2097,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2247,6 +2268,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2256,7 +2280,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2427,6 +2451,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2443,11 +2470,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="423729024"/>
-        <c:axId val="436425088"/>
+        <c:axId val="395157504"/>
+        <c:axId val="417242112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="423729024"/>
+        <c:axId val="395157504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2490,14 +2517,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436425088"/>
+        <c:crossAx val="417242112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="436425088"/>
+        <c:axId val="417242112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2548,12 +2575,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="423729024"/>
+        <c:crossAx val="395157504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="436426624"/>
+        <c:axId val="417354496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2590,12 +2617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438347264"/>
+        <c:crossAx val="417356800"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="438347264"/>
+        <c:axId val="417356800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2604,7 +2631,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="436426624"/>
+        <c:crossAx val="417354496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3013,7 +3040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5694,6 +5721,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:13" ht="12.75">
+      <c r="A60" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="12">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="12">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="13">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="13">
+        <v>-153850.30177591741</v>
+      </c>
+      <c r="F60" s="14">
+        <v>-146803.72614120715</v>
+      </c>
+      <c r="G60" s="14">
+        <v>13110889.927871184</v>
+      </c>
+      <c r="H60" s="14">
+        <v>13740212.356828064</v>
+      </c>
+      <c r="I60" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J60" s="14">
+        <v>15650423.858476061</v>
+      </c>
+      <c r="K60" s="14">
+        <v>5212099.6765850689</v>
+      </c>
+      <c r="L60" s="13">
+        <v>1910211.5016479976</v>
+      </c>
+      <c r="M60" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -615,6 +615,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -624,7 +627,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -797,6 +800,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -840,7 +846,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1014,6 +1020,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1023,7 +1032,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1197,6 +1206,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>15650423.858476061</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17341729.54692129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1239,7 +1251,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1413,6 +1425,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1422,7 +1437,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1596,6 +1611,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5212099.6765850689</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6903405.365030298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1617,11 +1635,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="367295872"/>
-        <c:axId val="385508864"/>
+        <c:axId val="457924608"/>
+        <c:axId val="457926144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="367295872"/>
+        <c:axId val="457924608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1664,14 +1682,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385508864"/>
+        <c:crossAx val="457926144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="385508864"/>
+        <c:axId val="457926144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1722,7 +1740,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="367295872"/>
+        <c:crossAx val="457924608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1883,7 +1901,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2057,6 +2075,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-153850.30177591741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-543896.52099822264</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,8 +2092,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="417356800"/>
-        <c:axId val="417354496"/>
+        <c:axId val="479004928"/>
+        <c:axId val="479003008"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2097,7 +2118,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2271,6 +2292,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2280,7 +2304,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2454,6 +2478,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2470,11 +2497,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395157504"/>
-        <c:axId val="417242112"/>
+        <c:axId val="472212224"/>
+        <c:axId val="472214144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395157504"/>
+        <c:axId val="472212224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2517,14 +2544,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417242112"/>
+        <c:crossAx val="472214144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="417242112"/>
+        <c:axId val="472214144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,12 +2602,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395157504"/>
+        <c:crossAx val="472212224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="417354496"/>
+        <c:axId val="479003008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2617,12 +2644,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417356800"/>
+        <c:crossAx val="479004928"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="417356800"/>
+        <c:axId val="479004928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2631,7 +2658,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="417354496"/>
+        <c:crossAx val="479003008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3040,7 +3067,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5762,6 +5789,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:13" ht="12.75">
+      <c r="A61" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="12">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="12">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="13">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="13">
+        <v>-543896.52099822264</v>
+      </c>
+      <c r="F61" s="14">
+        <v>-462104.07803294534</v>
+      </c>
+      <c r="G61" s="14">
+        <v>12648785.849838238</v>
+      </c>
+      <c r="H61" s="14">
+        <v>14887621.524275072</v>
+      </c>
+      <c r="I61" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J61" s="14">
+        <v>17341729.54692129</v>
+      </c>
+      <c r="K61" s="14">
+        <v>6903405.365030298</v>
+      </c>
+      <c r="L61" s="13">
+        <v>2454108.0226462204</v>
+      </c>
+      <c r="M61" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(SAR).xlsx
@@ -441,7 +441,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -618,6 +618,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -627,7 +630,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -803,6 +806,9 @@
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10438324.181890992</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10438324.181890992</c:v>
                 </c:pt>
               </c:numCache>
@@ -846,7 +852,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1023,6 +1029,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1032,7 +1041,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1209,6 +1218,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>17341729.54692129</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>18201846.466008939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1251,7 +1263,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1428,6 +1440,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1437,7 +1452,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1614,6 +1629,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6903405.365030298</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7763522.2841179464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1635,11 +1653,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="457924608"/>
-        <c:axId val="457926144"/>
+        <c:axId val="99720192"/>
+        <c:axId val="103724160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="457924608"/>
+        <c:axId val="99720192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1682,14 +1700,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="457926144"/>
+        <c:crossAx val="103724160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="457926144"/>
+        <c:axId val="103724160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1740,7 +1758,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="457924608"/>
+        <c:crossAx val="99720192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1901,7 +1919,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2078,6 +2096,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-543896.52099822264</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-658295.54002827872</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2092,8 +2113,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="479004928"/>
-        <c:axId val="479003008"/>
+        <c:axId val="424744832"/>
+        <c:axId val="399842304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2118,7 +2139,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2295,6 +2316,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2304,7 +2328,7 @@
               <c:f>'model4(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2481,6 +2505,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2497,11 +2524,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472212224"/>
-        <c:axId val="472214144"/>
+        <c:axId val="399531392"/>
+        <c:axId val="399840384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472212224"/>
+        <c:axId val="399531392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2544,14 +2571,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472214144"/>
+        <c:crossAx val="399840384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472214144"/>
+        <c:axId val="399840384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,12 +2629,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472212224"/>
+        <c:crossAx val="399531392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="479003008"/>
+        <c:axId val="399842304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,12 +2671,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479004928"/>
+        <c:crossAx val="424744832"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="479004928"/>
+        <c:axId val="424744832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2658,7 +2685,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="479003008"/>
+        <c:crossAx val="399842304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3067,7 +3094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5830,6 +5857,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:13" ht="12.75">
+      <c r="A62" s="11">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="12">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="12">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="13">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="13">
+        <v>-658295.54002827872</v>
+      </c>
+      <c r="F62" s="14">
+        <v>-528751.43574859062</v>
+      </c>
+      <c r="G62" s="14">
+        <v>12120034.414089648</v>
+      </c>
+      <c r="H62" s="14">
+        <v>15089442.903334439</v>
+      </c>
+      <c r="I62" s="14">
+        <v>10438324.181890992</v>
+      </c>
+      <c r="J62" s="14">
+        <v>18201846.466008939</v>
+      </c>
+      <c r="K62" s="14">
+        <v>7763522.2841179464</v>
+      </c>
+      <c r="L62" s="13">
+        <v>3112403.5626744991</v>
+      </c>
+      <c r="M62" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">
